--- a/Statistics/200m Bryst_statistics.xlsx
+++ b/Statistics/200m Bryst_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,20 +856,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.35,45</t>
+          <t>2.34,26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05.12.2021</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -891,20 +891,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ole Skuseth</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.36,03</t>
+          <t>2.35,45</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>05.12.2021</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -926,25 +926,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brage Wetjen Sigernes</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.36,83</t>
+          <t>2.36,03</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>01.12.2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -961,25 +961,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Morten Olden Larsen</t>
+          <t>Brage Wetjen Sigernes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.37,56</t>
+          <t>2.36,83</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06.12.2015</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -996,25 +996,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Morten Olden Larsen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.38,04</t>
+          <t>2.37,56</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>06.12.2015</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1031,25 +1031,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.38,12</t>
+          <t>2.38,04</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>03.10.2015</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1066,25 +1066,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.39,39</t>
+          <t>2.38,12</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11.02.2017</t>
+          <t>03.10.2015</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1101,20 +1101,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Simen Løvås</t>
+          <t>Eirik Hakvåg-Sandengen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.39,48</t>
+          <t>2.38,26</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05.12.2021</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1136,25 +1136,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maxim Sergeevich Gorodkov</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.40,12</t>
+          <t>2.39,39</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>11.02.2017</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1171,20 +1171,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ådne Viken Refseth</t>
+          <t>Simen Løvås</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.40,66</t>
+          <t>2.39,48</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21.03.2015</t>
+          <t>05.12.2021</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1206,25 +1206,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Maxim Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.42,29</t>
+          <t>2.40,12</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1241,25 +1241,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Ådne Viken Refseth</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.02,98</t>
+          <t>2.40,66</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04.12.2016</t>
+          <t>21.03.2015</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volda</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1276,25 +1276,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thais Farias Kristiansen</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3.04,06</t>
+          <t>3.02,98</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>09.06.2019</t>
+          <t>04.12.2016</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Klepp</t>
+          <t>Volda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1311,25 +1311,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.44,90</t>
+          <t>2.43,69</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08.06.2025</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1346,25 +1346,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Thais Farias Kristiansen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.45,09</t>
+          <t>3.04,06</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>04.10.2014</t>
+          <t>09.06.2019</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Klepp</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1381,25 +1381,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Eirik Hakvåg-Sandengen</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.45,56</t>
+          <t>2.44,90</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>03.12.2023</t>
+          <t>08.06.2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1416,25 +1416,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vetle Henriksen</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.45,96</t>
+          <t>2.45,09</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14.11.2009</t>
+          <t>04.10.2014</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1451,25 +1451,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hans Ourson Liem</t>
+          <t>Vetle Henriksen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.46,62</t>
+          <t>2.45,96</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>14.11.2009</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1486,25 +1486,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.47,14</t>
+          <t>2.46,09</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1521,25 +1521,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Hans Ourson Liem</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.48,07</t>
+          <t>2.46,62</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>06.04.2013</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fauske</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1591,25 +1591,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Leo Petter Hauge Sølvberg</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.49,12</t>
+          <t>2.48,07</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15.01.2017</t>
+          <t>06.04.2013</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fauske</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1626,25 +1626,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Leo Petter Hauge Sølvberg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3.10,08</t>
+          <t>2.49,12</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>15.01.2017</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1661,25 +1661,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.51,26</t>
+          <t>3.10,08</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1696,25 +1696,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kristin Myhr Pettersen</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3.12,12</t>
+          <t>2.51,26</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1731,25 +1731,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jon Olav Båtbukt</t>
+          <t>Kristin Myhr Pettersen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.52,45</t>
+          <t>3.12,12</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1766,25 +1766,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.52,40</t>
+          <t>2.51,96</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24.09.2016</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1801,25 +1801,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Simon Moe</t>
+          <t>Jon Olav Båtbukt</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.52,60</t>
+          <t>2.52,45</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>06.02.2016</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1836,25 +1836,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.52,83</t>
+          <t>2.52,40</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>24.09.2016</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1871,25 +1871,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Simon Moe</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.53,13</t>
+          <t>2.52,60</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>06.02.2016</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jonas Fiskaa Barstad</t>
+          <t>Simon Perssønn Mørseth</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.53,24</t>
+          <t>2.53,23</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1976,12 +1976,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Simon Perssønn Mørseth</t>
+          <t>Jonas Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.53,23</t>
+          <t>2.53,24</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2081,20 +2081,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.56,31</t>
+          <t>2.55,11</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12.05.2007</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2116,25 +2116,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jostein Ven</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2.56,62</t>
+          <t>2.56,31</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>12.05.2007</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2151,20 +2151,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Birk Skaalvik Trelstad</t>
+          <t>Jostein Ven</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.57,11</t>
+          <t>2.56,62</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2186,25 +2186,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Birk Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.57,25</t>
+          <t>2.57,11</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2221,25 +2221,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.57,49</t>
+          <t>2.57,25</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2256,20 +2256,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.57,91</t>
+          <t>2.57,49</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2291,7 +2291,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oliver Grøtte Ramstad</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20.10.2024</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2326,25 +2326,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Oliver Grøtte Ramstad</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.58,55</t>
+          <t>2.57,91</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>20.10.2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2361,25 +2361,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.59,23</t>
+          <t>2.58,55</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04.09.2021</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2396,25 +2396,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dhanushi Attanapola</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3.21,13</t>
+          <t>2.59,23</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>04.09.2021</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2431,25 +2431,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sander Haugan</t>
+          <t>Dhanushi Attanapola</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.00,48</t>
+          <t>3.21,13</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,25 +2466,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Sander Haugan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.00,62</t>
+          <t>3.00,48</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>04.12.2010</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2501,25 +2501,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.03,19</t>
+          <t>3.00,62</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>04.12.2010</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2536,25 +2536,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3.04,13</t>
+          <t>3.01,43</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>05.12.2021</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2571,25 +2571,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3.04,15</t>
+          <t>3.02,06</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2606,25 +2606,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3.04,36</t>
+          <t>3.04,13</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>05.12.2021</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2641,25 +2641,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elian Theodor Kringstad</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3.04,49</t>
+          <t>3.04,15</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2676,25 +2676,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Elian Theodor Kringstad</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3.04,89</t>
+          <t>3.04,49</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Joakim I. Larsen</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3.04,97</t>
+          <t>3.04,89</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12.01.2007</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2746,25 +2746,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Joakim I. Larsen</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.05,30</t>
+          <t>3.04,97</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>12.01.2007</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2781,25 +2781,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3.05,63</t>
+          <t>3.05,11</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2816,25 +2816,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3.05,88</t>
+          <t>3.05,30</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08.03.2008</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2851,25 +2851,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Even Kristoffer Lind Bøckman</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3.05,90</t>
+          <t>3.05,63</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2886,25 +2886,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3.06,57</t>
+          <t>3.05,88</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>08.03.2008</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2921,16 +2921,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Even Kristoffer Lind Bøckman</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3.06,59</t>
+          <t>3.05,90</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2956,25 +2956,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tor Arne Hegvik</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3.06,64</t>
+          <t>3.06,59</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2991,25 +2991,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stian Nilsen</t>
+          <t>Liv Løfaldli</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3.07,11</t>
+          <t>3.25,97</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>13.02.2010</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3026,20 +3026,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Tor Arne Hegvik</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3.07,65</t>
+          <t>3.06,64</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3061,25 +3061,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3.07,76</t>
+          <t>3.26,48</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18.01.2015</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3096,25 +3096,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kristin Stallvik</t>
+          <t>Stian Nilsen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3.31,42</t>
+          <t>3.07,11</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09.03.2019</t>
+          <t>13.02.2010</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3131,25 +3131,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Edvin Aurstad Bergum</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3.09,20</t>
+          <t>3.07,49</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3166,25 +3166,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3.31,69</t>
+          <t>3.07,76</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>18.01.2015</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3201,20 +3201,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3.09,52</t>
+          <t>3.07,65</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3236,25 +3236,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Kristin Stallvik</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3.09,50</t>
+          <t>3.31,42</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>09.03.2019</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3271,25 +3271,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Edvin Aurstad Bergum</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3.09,70</t>
+          <t>3.09,20</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3306,25 +3306,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Elias Hauge Lien</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3.11,41</t>
+          <t>3.31,69</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3341,25 +3341,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Liv Løfaldli</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3.34,76</t>
+          <t>3.09,52</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>18.04.2021</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3376,25 +3376,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lionel Nicolas Weissbrodt</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.11,86</t>
+          <t>3.09,50</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3411,20 +3411,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3.12,16</t>
+          <t>3.09,70</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3446,20 +3446,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Lev Shestov</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3.12,23</t>
+          <t>3.10,11</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3481,20 +3481,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Elias Hauge Lien</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3.12,97</t>
+          <t>3.11,41</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3516,25 +3516,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Lionel Nicolas Weissbrodt</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3.38,22</t>
+          <t>3.11,86</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3551,25 +3551,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3.15,22</t>
+          <t>3.12,16</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3586,25 +3586,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3.15,33</t>
+          <t>3.12,23</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3621,25 +3621,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.15,83</t>
+          <t>3.12,42</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3656,20 +3656,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Carl Victor Mukisa Nygård</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.15,88</t>
+          <t>3.12,97</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3691,20 +3691,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3.16,22</t>
+          <t>3.38,22</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>04.10.2014</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3726,25 +3726,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.16,47</t>
+          <t>3.15,22</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>30.09.2023</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3761,25 +3761,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.16,73</t>
+          <t>3.15,33</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3796,25 +3796,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3.17,15</t>
+          <t>3.15,83</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3831,20 +3831,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Terje Martin Lundahl</t>
+          <t>Carl Victor Mukisa Nygård</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.18,59</t>
+          <t>3.15,88</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3866,25 +3866,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3.18,79</t>
+          <t>3.16,22</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>04.10.2014</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3901,25 +3901,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3.19,06</t>
+          <t>3.16,19</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3936,20 +3936,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.19,11</t>
+          <t>3.16,47</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>30.09.2023</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3971,25 +3971,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Setareh Kulsum Sigrid Feyzi</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3.44,23</t>
+          <t>3.16,73</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4006,20 +4006,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Johannes Tryggestad</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3.20,20</t>
+          <t>3.17,15</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4041,25 +4041,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>Terje Martin Lundahl</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3.21,70</t>
+          <t>3.18,59</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4076,25 +4076,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.21,67</t>
+          <t>3.18,79</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4111,25 +4111,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kristian Myhr Høgstøl</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.21,64</t>
+          <t>3.19,11</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4146,25 +4146,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Victor Voormolen Gutierrez</t>
+          <t>Johannes Tryggestad</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.22,65</t>
+          <t>3.20,20</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4181,25 +4181,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Setareh Kulsum Sigrid Feyzi</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.23,12</t>
+          <t>3.44,23</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>29.09.2018</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4216,25 +4216,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Kristian Myhr Høgstøl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.48,39</t>
+          <t>3.21,64</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4251,20 +4251,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Finn Øivind Fevang</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.23,96</t>
+          <t>3.21,67</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>16.01.2005</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4286,25 +4286,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.24,47</t>
+          <t>3.21,70</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4321,25 +4321,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.27,19</t>
+          <t>3.22,00</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>04.12.2016</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4356,25 +4356,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Emily Liv Liem</t>
+          <t>Victor Voormolen Gutierrez</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.53,04</t>
+          <t>3.22,65</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4391,20 +4391,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kaan Baltaci</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3.28,09</t>
+          <t>3.23,97</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01.10.2022</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4426,25 +4426,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ailin Østerås</t>
+          <t>Finn Øivind Fevang</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3.53,35</t>
+          <t>3.23,96</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12.03.2011</t>
+          <t>16.01.2005</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4461,25 +4461,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3.28,33</t>
+          <t>3.27,19</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>04.12.2016</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4496,20 +4496,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Kaan Baltaci</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.29,20</t>
+          <t>3.28,09</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>01.10.2022</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4531,20 +4531,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Emily Liv Liem</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3.30,04</t>
+          <t>3.53,04</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4566,25 +4566,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Ailin Østerås</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.31,10</t>
+          <t>3.53,35</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>12.03.2011</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4601,25 +4601,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3.34,14</t>
+          <t>3.29,36</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>30.10.2010</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4636,20 +4636,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Conrad Sippala Hassel</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.34,84</t>
+          <t>3.29,20</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4671,25 +4671,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4.02,00</t>
+          <t>3.30,04</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4706,25 +4706,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Marcus Thalberg Fagerheim</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3.36,59</t>
+          <t>3.31,10</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>28.04.2012</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4746,20 +4746,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.37,93</t>
+          <t>3.32,03</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4776,25 +4776,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tymofii Dzisiak</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3.37,97</t>
+          <t>3.33,87</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4811,20 +4811,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Even Greiff</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.38,69</t>
+          <t>3.34,14</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>30.10.2010</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4846,25 +4846,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.39,41</t>
+          <t>3.56,44</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>04.10.2014</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4881,20 +4881,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Conrad Sippala Hassel</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.39,29</t>
+          <t>3.34,84</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4916,25 +4916,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.40,74</t>
+          <t>3.36,21</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4951,16 +4951,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3.41,61</t>
+          <t>4.02,00</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4986,25 +4986,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lyder Ringsvold Hogstad</t>
+          <t>Marcus Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.41,58</t>
+          <t>3.36,59</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>28.04.2012</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5021,25 +5021,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Christopher Janjua</t>
+          <t>Tymofii Dzisiak</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3.42,22</t>
+          <t>3.37,97</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>19.03.2006</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5056,25 +5056,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Olav Høyland Hofstad</t>
+          <t>Even Greiff</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.42,27</t>
+          <t>3.38,69</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5091,16 +5091,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.45,59</t>
+          <t>3.39,41</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -5126,25 +5126,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4.12,82</t>
+          <t>3.39,29</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5161,20 +5161,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Einar Risholt Moen</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3.47,08</t>
+          <t>3.39,72</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5196,25 +5196,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>Lyder Ringsvold Hogstad</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3.47,66</t>
+          <t>3.41,58</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5231,25 +5231,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Ingeborg Vold Kirkvold</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3.48,44</t>
+          <t>4.04,69</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>06.12.2008</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5266,20 +5266,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Christopher Janjua</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4.15,91</t>
+          <t>3.42,22</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12.02.2011</t>
+          <t>19.03.2006</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5301,20 +5301,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.52,15</t>
+          <t>3.45,59</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>04.10.2014</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5336,25 +5336,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Einar Risholt Moen</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3.52,83</t>
+          <t>3.47,08</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5371,20 +5371,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.55,56</t>
+          <t>4.11,48</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5406,25 +5406,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3.57,43</t>
+          <t>4.15,91</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>22.10.2022</t>
+          <t>12.02.2011</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5441,25 +5441,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Voormolen Gutierrez Victor</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.58,96</t>
+          <t>3.48,44</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>06.12.2008</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5476,25 +5476,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Peder Lund Juul</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3.58,71</t>
+          <t>4.14,72</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5511,25 +5511,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.59,09</t>
+          <t>3.52,15</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5546,20 +5546,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Angelico Mikkel Andersen</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4.00,41</t>
+          <t>3.53,36</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5581,20 +5581,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4.00,87</t>
+          <t>3.55,56</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5616,25 +5616,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Idun Skjærseth</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4.30,74</t>
+          <t>3.57,43</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>22.10.2022</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5651,25 +5651,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Peder Lund Juul</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4.04,07</t>
+          <t>3.58,71</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5686,20 +5686,20 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Vår Kristine Sollien Skar</t>
+          <t>Voormolen Gutierrez Victor</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4.34,19</t>
+          <t>3.58,96</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5721,25 +5721,25 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Leo Alexander Farias Kristiansen</t>
+          <t>Torben Bräuer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4.04,97</t>
+          <t>3.58,60</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5756,20 +5756,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Angelico Mikkel Andersen</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4.07,53</t>
+          <t>4.00,41</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5791,25 +5791,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Idun Skjærseth</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4.08,99</t>
+          <t>4.30,74</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>28.02.2009</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5826,20 +5826,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4.09,92</t>
+          <t>4.04,07</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5861,20 +5861,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Robert Andre Skarø</t>
+          <t>Leo Alexander Farias Kristiansen</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4.10,22</t>
+          <t>4.04,97</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5896,20 +5896,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Nikan Ommani</t>
+          <t>Vår Kristine Sollien Skar</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4.10,73</t>
+          <t>4.34,19</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5931,20 +5931,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sigurd Kristoffersen Torvik</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4.11,63</t>
+          <t>4.07,53</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5966,25 +5966,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Brage Kaminka Heiberg</t>
+          <t>Magnus Hestvik Larsen</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4.12,38</t>
+          <t>4.08,99</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>16.09.2023</t>
+          <t>28.02.2009</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6001,20 +6001,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Morten Johansen</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4.14,03</t>
+          <t>4.09,92</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>14.01.2006</t>
+          <t>18.04.2021</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6036,25 +6036,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jesper Øvermo Johansen</t>
+          <t>Nikan Ommani</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4.14,21</t>
+          <t>4.10,73</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6071,25 +6071,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ingeborg Vold Kirkvold</t>
+          <t>Robert Andre Skarø</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4.48,98</t>
+          <t>4.10,22</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6106,20 +6106,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Hauk Vold Kirkvold</t>
+          <t>Sigurd Kristoffersen Torvik</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4.29,40</t>
+          <t>4.11,63</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6141,25 +6141,25 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Casper Dahle-Øfsti</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>4.37,59</t>
+          <t>4.12,30</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20.10.2013</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6176,25 +6176,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Brage Kaminka Heiberg</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4.45,24</t>
+          <t>4.12,38</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>16.09.2023</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6211,20 +6211,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Gajithsing Ajeethsing</t>
+          <t>Morten Johansen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5.13,32</t>
+          <t>4.14,03</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>14.01.2006</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6246,20 +6246,20 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Theodor Hoff</t>
+          <t>Ragnhild Fjermestad</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5.17,69</t>
+          <t>4.40,69</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6281,33 +6281,418 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>Jesper Øvermo Johansen</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4.14,21</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>105</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>25.10.2020</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guy Løfaldli</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4.23,11</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>95</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>30.11.2025</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hauk Vold Kirkvold</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4.29,40</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>88</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>18.04.2021</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Barnaby Lee_Wright</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>4.36,94</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>81</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Casper Dahle-Øfsti</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>4.37,59</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>81</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>20.10.2013</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Emil Falkenbo-Skalmerås</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>4.38,85</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>80</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Hans Otto Søyseth</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4.45,24</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>74</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>29.11.2014</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Noah Kvam Haaheim</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4.54,06</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>68</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Brage Hetling</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5.06,82</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>60</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Gajithsing Ajeethsing</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5.13,32</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>56</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>19.06.2021</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Theodor Hoff</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5.17,69</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>54</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>03.11.2012</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
           <t>Riccardo Manum</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>5.40,11</t>
         </is>
       </c>
-      <c r="C168" t="n">
+      <c r="C179" t="n">
         <v>44</v>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>19.01.2025</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -7522,12 +7907,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3.18,45</t>
+          <t>3.18,58</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -7535,7 +7920,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14.06.2008</t>
+          <t>15.06.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -7557,12 +7942,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3.18,58</t>
+          <t>3.18,45</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7570,7 +7955,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>14.06.2008</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -8082,12 +8467,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3.50,70</t>
+          <t>3.50,98</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -8095,7 +8480,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>01.05.2022</t>
+          <t>15.06.2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -8117,12 +8502,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3.50,98</t>
+          <t>3.50,70</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -8130,7 +8515,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>01.05.2022</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8510,7 +8895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9183,25 +9568,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.55,94</t>
+          <t>2.52,80</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>25.10.2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -9218,12 +9603,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Signe Hogstad</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.55,87</t>
+          <t>2.55,94</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -9231,7 +9616,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.03.2025</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9253,25 +9638,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maud Steinsdotter Nestgaard</t>
+          <t>Signe Hogstad</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.56,34</t>
+          <t>2.55,87</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06.02.2016</t>
+          <t>29.03.2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -9288,25 +9673,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Christiana Bjørkli</t>
+          <t>Maud Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.56,50</t>
+          <t>2.56,34</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06.10.2007</t>
+          <t>06.02.2016</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -9323,20 +9708,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Elisabeth Wilmann</t>
+          <t>Christiana Bjørkli</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.57,86</t>
+          <t>2.56,50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>06.10.2007</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -9358,20 +9743,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Elisabeth Wilmann</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.58,52</t>
+          <t>2.57,86</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -9393,25 +9778,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.58,67</t>
+          <t>2.58,52</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -9428,25 +9813,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.59,15</t>
+          <t>2.58,67</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11.02.2012</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9463,25 +9848,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Julie Hegvik</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3.00,15</t>
+          <t>2.59,15</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>11.02.2012</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9498,25 +9883,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.00,61</t>
+          <t>2.56,90</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9533,20 +9918,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ingrid Johansen</t>
+          <t>Julie Hegvik</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3.00,85</t>
+          <t>3.00,15</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>06.10.2007</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -9568,25 +9953,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3.01,34</t>
+          <t>3.00,61</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>08.06.2025</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9603,20 +9988,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maria Bøe</t>
+          <t>Ingrid Johansen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3.02,33</t>
+          <t>3.00,85</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.01.2011</t>
+          <t>06.10.2007</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -9638,25 +10023,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Silje Aadahl</t>
+          <t>Maria Bøe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.02,50</t>
+          <t>3.02,33</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30.09.2017</t>
+          <t>23.01.2011</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9673,25 +10058,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Karoline Volden</t>
+          <t>Silje Aadahl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.02,83</t>
+          <t>3.02,50</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02.04.2016</t>
+          <t>30.09.2017</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mandal</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9708,25 +10093,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Inga Maren Steinsdotter Nestgaard</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3.03,60</t>
+          <t>2.59,82</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>04.12.2016</t>
+          <t>25.10.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9743,25 +10128,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Frøydis Vatn Andersen</t>
+          <t>Karoline Volden</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3.04,45</t>
+          <t>3.02,83</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.02.2017</t>
+          <t>02.04.2016</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Mandal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9778,25 +10163,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Viktoria Juel</t>
+          <t>Inga Maren Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3.04,38</t>
+          <t>3.03,60</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12.02.2011</t>
+          <t>04.12.2016</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9813,25 +10198,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Viktoria Juel</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3.04,91</t>
+          <t>3.04,38</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>12.02.2011</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9848,25 +10233,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vincente Quiles Saez</t>
+          <t>Frøydis Vatn Andersen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.46,23</t>
+          <t>3.04,45</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>11.02.2017</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -9883,12 +10268,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nora Yian Baldersheim</t>
+          <t>Vincente Quiles Saez</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3.06,21</t>
+          <t>2.46,23</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -9896,12 +10281,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -9918,16 +10303,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Karoline Borg Simonsen</t>
+          <t>Nora Yian Baldersheim</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3.06,91</t>
+          <t>3.06,21</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9953,12 +10338,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solveig Natvig Løvseth</t>
+          <t>Karoline Borg Simonsen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3.06,87</t>
+          <t>3.06,91</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -9966,12 +10351,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9988,25 +10373,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hege Solberg Jørgensen</t>
+          <t>Solveig Natvig Løvseth</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3.07,57</t>
+          <t>3.06,87</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -10023,20 +10408,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3.07,81</t>
+          <t>3.07,57</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -10058,25 +10443,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.08,05</t>
+          <t>3.07,81</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04.09.2021</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -10093,25 +10478,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.08,31</t>
+          <t>3.08,05</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>04.09.2021</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -10128,25 +10513,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3.09,65</t>
+          <t>3.08,31</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10163,25 +10548,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Helle Krogstad</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3.09,94</t>
+          <t>3.09,65</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -10198,25 +10583,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Helle Krogstad</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.10,19</t>
+          <t>3.09,94</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.03.2006</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -10268,25 +10653,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3.10,36</t>
+          <t>3.10,19</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.03.2006</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10303,25 +10688,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marie Skuseth</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3.10,61</t>
+          <t>3.10,36</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10338,25 +10723,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3.11,49</t>
+          <t>3.07,49</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>30.09.2017</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10373,25 +10758,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3.11,38</t>
+          <t>3.10,61</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10408,20 +10793,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3.12,40</t>
+          <t>3.11,38</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10443,25 +10828,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.12,58</t>
+          <t>3.11,49</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>30.09.2017</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10478,25 +10863,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3.12,58</t>
+          <t>3.12,40</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10513,20 +10898,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Edle Lund</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.12,78</t>
+          <t>3.12,58</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11.02.2017</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -10548,20 +10933,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Edle Lund</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.13,37</t>
+          <t>3.12,78</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>11.02.2017</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -10583,25 +10968,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.14,00</t>
+          <t>3.13,37</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -10618,25 +11003,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ingrid Elverum</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3.14,43</t>
+          <t>3.14,00</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -10653,12 +11038,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Ingrid Elverum</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3.14,40</t>
+          <t>3.14,43</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -10666,12 +11051,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -10688,25 +11073,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Embla Mimi Baarholm</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3.15,29</t>
+          <t>3.14,40</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -10723,25 +11108,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Anette Haugsbakk Fløan</t>
+          <t>Embla Mimi Baarholm</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3.15,49</t>
+          <t>3.15,29</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>24.06.2007</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -10758,20 +11143,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Anette Haugsbakk Fløan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3.15,72</t>
+          <t>3.15,49</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>24.06.2007</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -10793,12 +11178,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3.15,60</t>
+          <t>3.15,72</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -10806,12 +11191,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -10828,25 +11213,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.15,81</t>
+          <t>3.15,60</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.06.2013</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -10863,12 +11248,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ada Viken Refseth</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3.15,80</t>
+          <t>3.15,81</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -10876,7 +11261,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>15.06.2013</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -10898,25 +11283,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Ada Viken Refseth</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3.16,31</t>
+          <t>3.15,80</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -11108,12 +11493,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3.18,60</t>
+          <t>3.18,44</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -11143,12 +11528,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3.18,44</t>
+          <t>3.18,60</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -11318,12 +11703,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Izabele Farias Ribeiro</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3.20,90</t>
+          <t>3.20,91</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -11331,12 +11716,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>06.02.2016</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -11353,12 +11738,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Izabele Farias Ribeiro</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3.20,91</t>
+          <t>3.20,92</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -11366,12 +11751,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>12.02.2022</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -11388,12 +11773,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3.20,92</t>
+          <t>3.20,90</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -11401,12 +11786,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>12.02.2022</t>
+          <t>06.02.2016</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -11458,12 +11843,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Miriam Vedvik</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.22,60</t>
+          <t>3.00,79</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -11471,12 +11856,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -11493,12 +11878,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3.00,79</t>
+          <t>3.22,44</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -11506,7 +11891,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>09.01.2015</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11528,12 +11913,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Miriam Vedvik</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3.22,44</t>
+          <t>3.22,60</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -11541,12 +11926,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>09.01.2015</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -11563,25 +11948,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3.24,21</t>
+          <t>3.20,03</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>21.10.2018</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -11598,12 +11983,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3.24,20</t>
+          <t>3.24,21</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -11611,12 +11996,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>21.03.2015</t>
+          <t>21.10.2018</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -11633,16 +12018,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3.24,57</t>
+          <t>3.24,20</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11668,25 +12053,25 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Olivia Sterud Prytz</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3.25,42</t>
+          <t>3.24,57</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>21.03.2015</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -11703,25 +12088,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Olivia Sterud Prytz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.25,87</t>
+          <t>3.25,42</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -11738,20 +12123,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vilde Austmo</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.26,63</t>
+          <t>3.25,87</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -11773,25 +12158,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Vilde Austmo</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3.05,92</t>
+          <t>3.26,63</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -11808,25 +12193,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.28,66</t>
+          <t>3.05,92</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -11843,25 +12228,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.29,13</t>
+          <t>3.28,66</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -11913,25 +12298,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Thea Haugan</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.29,65</t>
+          <t>3.29,13</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11948,25 +12333,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Thea Haugan</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3.30,53</t>
+          <t>3.29,65</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -12123,12 +12508,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Amalie Solvoll</t>
+          <t>Sofie Hoff</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3.34,11</t>
+          <t>3.33,91</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -12136,12 +12521,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -12158,12 +12543,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sofie Hoff</t>
+          <t>Amalie Solvoll</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.33,91</t>
+          <t>3.34,11</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -12171,12 +12556,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12193,12 +12578,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Anna Svendsen</t>
+          <t>Marte Hemmer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.34,37</t>
+          <t>3.34,38</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -12206,12 +12591,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>16.01.2005</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -12228,12 +12613,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Marte Hemmer</t>
+          <t>Anna Svendsen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.34,38</t>
+          <t>3.34,37</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -12241,12 +12626,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>16.01.2005</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -12263,12 +12648,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.34,99</t>
+          <t>3.35,02</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -12276,12 +12661,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19.04.2009</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -12298,12 +12683,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.35,02</t>
+          <t>3.34,99</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -12311,12 +12696,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.04.2009</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -12333,25 +12718,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Julie Wiik Arnesen</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.36,47</t>
+          <t>3.32,41</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -12368,25 +12753,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sara Skaalvik Trelstad</t>
+          <t>Julie Wiik Arnesen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.37,50</t>
+          <t>3.36,47</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -12403,25 +12788,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Alice Sophie Mittet</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.38,04</t>
+          <t>3.34,10</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>21.01.2018</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -12438,25 +12823,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Sara Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.39,90</t>
+          <t>3.37,50</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.01.2014</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -12473,20 +12858,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Alice Sophie Mittet</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3.17,62</t>
+          <t>3.38,04</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>21.01.2018</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12508,20 +12893,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sigrid Moen Henriksen</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3.41,96</t>
+          <t>3.34,90</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12543,25 +12928,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Aurora Moen Wannebo</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3.42,54</t>
+          <t>3.17,62</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -12578,25 +12963,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mia Bretun Finserå</t>
+          <t>Sigrid Moen Henriksen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.42,52</t>
+          <t>3.41,96</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -12613,25 +12998,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Aurora Moen Wannebo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3.43,20</t>
+          <t>3.42,54</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -12648,25 +13033,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Mia Bretun Finserå</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.44,88</t>
+          <t>3.42,52</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -12683,25 +13068,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3.45,15</t>
+          <t>3.43,20</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -12718,12 +13103,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Victoria Dessen</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.45,32</t>
+          <t>3.45,15</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -12731,12 +13116,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>01.12.2024</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -12753,25 +13138,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Madeleine Tran Wæraas</t>
+          <t>Victoria Dessen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.46,55</t>
+          <t>3.45,32</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>27.10.2019</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -12788,20 +13173,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Madeleine Tran Wæraas</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3.46,80</t>
+          <t>3.46,55</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12.02.2005</t>
+          <t>27.10.2019</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12823,25 +13208,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Line Steine Bertelsen</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.47,80</t>
+          <t>3.46,80</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>12.02.2005</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -12858,20 +13243,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Aurora S. Juel</t>
+          <t>Line Steine Bertelsen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3.48,13</t>
+          <t>3.47,80</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>06.10.2012</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12893,20 +13278,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pia Helena Wildhagen</t>
+          <t>Aurora S. Juel</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.48,75</t>
+          <t>3.48,13</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>21.01.2018</t>
+          <t>06.10.2012</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12928,25 +13313,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Camila Dorao</t>
+          <t>Kristina Aleman Sandsund</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3.49,39</t>
+          <t>3.44,63</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -12963,25 +13348,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.52,74</t>
+          <t>3.44,75</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -12998,20 +13383,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Pia Helena Wildhagen</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.53,50</t>
+          <t>3.48,75</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>21.01.2018</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -13033,25 +13418,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cathrine Hegle</t>
+          <t>Camila Dorao</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>3.54,07</t>
+          <t>3.49,39</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>12.02.2011</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -13068,25 +13453,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.54,79</t>
+          <t>3.52,74</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>19.03.2006</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -13103,20 +13488,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>3.55,69</t>
+          <t>3.53,50</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13138,20 +13523,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Luma Nicole Farias Kristiansen</t>
+          <t>Cathrine Hegle</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.57,53</t>
+          <t>3.54,07</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>12.02.2011</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13173,25 +13558,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.57,94</t>
+          <t>3.54,79</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.03.2006</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -13208,20 +13593,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Phoebe Thalberg Fagerheim</t>
+          <t>Ramona Vutudal</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.59,64</t>
+          <t>3.55,69</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>13.01.2013</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13243,20 +13628,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3.59,58</t>
+          <t>3.52,75</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -13278,25 +13663,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kaia Winnberg</t>
+          <t>Luma Nicole Farias Kristiansen</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4.00,10</t>
+          <t>3.57,53</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -13313,25 +13698,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Phoebe Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4.00,26</t>
+          <t>3.59,64</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>13.01.2013</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -13348,25 +13733,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Kaia Winnberg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4.01,07</t>
+          <t>4.00,10</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>01.12.2024</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -13383,25 +13768,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kristina Bragadottir</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4.02,46</t>
+          <t>4.00,26</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>16.06.2012</t>
+          <t>01.12.2024</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -13418,25 +13803,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4.03,14</t>
+          <t>3.57,58</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -13453,20 +13838,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4.05,17</t>
+          <t>3.59,07</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13488,25 +13873,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Tora Tveiten</t>
+          <t>Kristina Bragadottir</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4.08,10</t>
+          <t>4.02,46</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>16.06.2012</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -13523,25 +13908,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Julia Beatrice Ferreira Kristiansen</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4.08,51</t>
+          <t>4.03,14</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>04.12.2016</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -13558,25 +13943,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>4.09,43</t>
+          <t>4.05,17</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>19.10.2019</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -13593,25 +13978,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ella Katrine Lind Bøckman</t>
+          <t>Tora Tveiten</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4.11,95</t>
+          <t>4.08,10</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -13628,25 +14013,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Camilla Gervasoni</t>
+          <t>Julia Beatrice Ferreira Kristiansen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4.16,77</t>
+          <t>4.08,51</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>04.12.2016</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -13663,25 +14048,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4.17,97</t>
+          <t>4.09,43</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>19.10.2019</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -13698,25 +14083,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Nicoline Vinje</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>4.19,03</t>
+          <t>4.07,42</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -13733,20 +14118,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Connie Rakel Lånke</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4.20,29</t>
+          <t>4.07,53</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>05.04.2014</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13768,25 +14153,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sara Olea  Riseth Moe</t>
+          <t>Ella Katrine Lind Bøckman</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4.20,86</t>
+          <t>4.11,95</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -13803,20 +14188,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Aurora Dahl Bere</t>
+          <t>Camilla Gervasoni</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4.22,35</t>
+          <t>4.16,77</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13838,25 +14223,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Hedda Gätzschmann</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4.25,77</t>
+          <t>4.19,03</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -13873,25 +14258,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Connie Rakel Lånke</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3.58,19</t>
+          <t>4.20,29</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>05.04.2014</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -13908,16 +14293,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Vilma Granhus Følstad</t>
+          <t>Sara Olea  Riseth Moe</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4.28,78</t>
+          <t>4.20,86</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13943,20 +14328,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Lea almaas</t>
+          <t>Aurora Dahl Bere</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4.30,27</t>
+          <t>4.22,35</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13978,25 +14363,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Klara Marie Gildemyn Strabac</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4.31,10</t>
+          <t>4.25,77</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20.09.2020</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -14013,20 +14398,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sanna Beckstrøm</t>
+          <t>Hanna Robertsen Burton</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>4.32,36</t>
+          <t>4.21,91</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>21.05.2005</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14048,20 +14433,20 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sunniva Eldholm</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4.33,39</t>
+          <t>3.58,19</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14083,20 +14468,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Live Hamnes Ulriksen</t>
+          <t>Vilma Granhus Følstad</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4.36,16</t>
+          <t>4.28,78</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14118,25 +14503,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ronja Emilia Wikström</t>
+          <t>Lea almaas</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4.45,91</t>
+          <t>4.30,27</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>11.02.2023</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -14153,20 +14538,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Elena Fyhn Leida</t>
+          <t>Klara Marie Gildemyn Strabac</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4.53,41</t>
+          <t>4.31,10</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>20.09.2020</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14188,20 +14573,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anna Fenstad Høysæter</t>
+          <t>Sanna Beckstrøm</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>4.54,04</t>
+          <t>4.32,36</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>21.05.2005</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14223,33 +14608,278 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>Sunniva Eldholm</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>4.33,39</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>119</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>18.04.2021</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Emilie Magnussen</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>4.38,31</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>107</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Charlotte Talseth</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>4.39,52</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>106</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Ronja Emilia Wikström</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>4.45,91</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>104</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>11.02.2023</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Hommelvik</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Elena Fyhn Leida</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>4.53,41</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>96</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>18.04.2021</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Anna Fenstad Høysæter</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>4.54,04</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>95</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>19.01.2020</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Aurora Aarflot Johannessen</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>4.54,51</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>91</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>Snorre Risholt Moen</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>4.49,68</t>
         </is>
       </c>
-      <c r="C164" t="n">
+      <c r="C171" t="n">
         <v>71</v>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>20.04.2013</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>Stjørdal</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -16409,12 +17039,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sigrid Moen Henriksen</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4.01,76</t>
+          <t>4.01,77</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -16422,12 +17052,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01.05.2022</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -16444,12 +17074,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Sigrid Moen Henriksen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4.01,77</t>
+          <t>4.01,76</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -16457,12 +17087,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>01.05.2022</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
